--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="293">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -811,7 +811,7 @@
     <t>Items can repeat in the answers, so a direct 1..1 correspondence by position might not exist - requiring correspondence by identifier.</t>
   </si>
   <si>
-    <t>resumen</t>
+    <t>Resumen</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=DEFN].target[classCode=OBS, moodCode=DEFN].id</t>
@@ -846,9 +846,6 @@
   </si>
   <si>
     <t>Allows the questionnaire response to be read without access to the questionnaire.</t>
-  </si>
-  <si>
-    <t>Resumen</t>
   </si>
   <si>
     <t>.text</t>
@@ -4144,7 +4141,7 @@
         <v>75</v>
       </c>
       <c r="R27" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -4201,7 +4198,7 @@
         <v>75</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4209,7 +4206,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4235,13 +4232,13 @@
         <v>230</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
@@ -4291,7 +4288,7 @@
         <v>75</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>73</v>
@@ -4309,7 +4306,7 @@
         <v>75</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
@@ -4317,7 +4314,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4423,7 +4420,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4531,7 +4528,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4641,7 +4638,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4664,19 +4661,19 @@
         <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="K32" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="K32" t="s" s="2">
+      <c r="L32" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>75</v>
@@ -4701,14 +4698,14 @@
         <v>75</v>
       </c>
       <c r="W32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="X32" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="X32" t="s" s="2">
+      <c r="Y32" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Y32" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="Z32" t="s" s="2">
         <v>75</v>
       </c>
@@ -4725,7 +4722,7 @@
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>73</v>
@@ -4743,7 +4740,7 @@
         <v>75</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -4751,7 +4748,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -4777,14 +4774,14 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>75</v>
@@ -4833,7 +4830,7 @@
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>73</v>
@@ -4859,7 +4856,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -4885,14 +4882,14 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>75</v>
@@ -4941,7 +4938,7 @@
         <v>75</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>73</v>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T18:46:21+00:00</t>
+    <t>2023-02-07T12:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
+++ b/refs/heads/main/StructureDefinition-QuestionnaireResponseInicioLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
